--- a/Model_zzy/results_milp.xlsx
+++ b/Model_zzy/results_milp.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2096.151070497497</v>
+        <v>2096.151070497498</v>
       </c>
     </row>
     <row r="30">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2228.613996074576</v>
+        <v>2228.613996074577</v>
       </c>
     </row>
     <row r="31">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2567.934877390614</v>
+        <v>2567.934877390615</v>
       </c>
     </row>
     <row r="38">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3319.465361866998</v>
+        <v>3319.465361866999</v>
       </c>
     </row>
     <row r="39">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3544.479091445881</v>
+        <v>3544.479091445882</v>
       </c>
     </row>
     <row r="41">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3047.437508220232</v>
+        <v>3047.437508220231</v>
       </c>
     </row>
     <row r="46">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3231.464631841385</v>
+        <v>3231.464631841384</v>
       </c>
     </row>
     <row r="48">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-403.6238171567554</v>
+        <v>-403.6238171567551</v>
       </c>
     </row>
     <row r="119">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1276.124641211556</v>
+        <v>1276.124641211555</v>
       </c>
     </row>
     <row r="132">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>798.3395030402437</v>
+        <v>798.3395030402434</v>
       </c>
     </row>
     <row r="133">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>202.701712923052</v>
+        <v>202.7017129230517</v>
       </c>
     </row>
     <row r="134">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>296.4984094972058</v>
+        <v>296.4984094972056</v>
       </c>
     </row>
     <row r="135">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>484.3096126782114</v>
+        <v>484.3096126782111</v>
       </c>
     </row>
     <row r="136">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>765.9472934528549</v>
+        <v>765.9472934528546</v>
       </c>
     </row>
     <row r="137">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>888.4121039147639</v>
+        <v>888.4121039147636</v>
       </c>
     </row>
     <row r="142">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>438.1643717549838</v>
+        <v>438.164371754984</v>
       </c>
     </row>
     <row r="143">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>531.4901430114739</v>
+        <v>531.4901430114741</v>
       </c>
     </row>
     <row r="144">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>403.6238171567554</v>
+        <v>403.6238171567551</v>
       </c>
     </row>
     <row r="191">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>92.84459028319998</v>
+        <v>92.84459028319999</v>
       </c>
     </row>
     <row r="230">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>74.88106126358036</v>
+        <v>74.88106126358035</v>
       </c>
     </row>
     <row r="378">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>74.88106126358036</v>
+        <v>74.88106126358035</v>
       </c>
     </row>
     <row r="402">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>504.6045490751615</v>
+        <v>504.6045490751618</v>
       </c>
     </row>
     <row r="411">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>504.2545490751614</v>
+        <v>504.2545490751617</v>
       </c>
     </row>
     <row r="412">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>503.9045490751615</v>
+        <v>503.9045490751618</v>
       </c>
     </row>
     <row r="413">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>503.5545490751614</v>
+        <v>503.5545490751617</v>
       </c>
     </row>
     <row r="414">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>503.2045490751614</v>
+        <v>503.2045490751618</v>
       </c>
     </row>
     <row r="415">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>502.8545490751615</v>
+        <v>502.8545490751619</v>
       </c>
     </row>
     <row r="416">
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>502.5045490751614</v>
+        <v>502.5045490751618</v>
       </c>
     </row>
     <row r="417">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>502.1545490751614</v>
+        <v>502.1545490751618</v>
       </c>
     </row>
     <row r="418">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>501.8045490751613</v>
+        <v>501.8045490751617</v>
       </c>
     </row>
     <row r="419">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>501.4545490751613</v>
+        <v>501.4545490751617</v>
       </c>
     </row>
     <row r="420">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751618</v>
       </c>
     </row>
     <row r="421">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>500.7545490751614</v>
+        <v>500.7545490751618</v>
       </c>
     </row>
     <row r="422">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751618</v>
       </c>
     </row>
     <row r="423">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751617</v>
       </c>
     </row>
     <row r="424">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751617</v>
       </c>
     </row>
     <row r="425">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751619</v>
       </c>
     </row>
     <row r="426">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751611</v>
       </c>
     </row>
     <row r="427">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>499.3545490751612</v>
+        <v>499.3545490751611</v>
       </c>
     </row>
     <row r="430">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>499.0045490751612</v>
+        <v>499.0045490751613</v>
       </c>
     </row>
     <row r="431">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>498.6545490751612</v>
+        <v>498.6545490751611</v>
       </c>
     </row>
     <row r="432">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>504.6045490751615</v>
+        <v>504.6045490751618</v>
       </c>
     </row>
     <row r="435">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>504.2545490751614</v>
+        <v>504.2545490751617</v>
       </c>
     </row>
     <row r="436">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>503.9045490751615</v>
+        <v>503.9045490751618</v>
       </c>
     </row>
     <row r="437">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>503.5545490751614</v>
+        <v>503.5545490751617</v>
       </c>
     </row>
     <row r="438">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>503.2045490751614</v>
+        <v>503.2045490751618</v>
       </c>
     </row>
     <row r="439">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>502.8545490751615</v>
+        <v>502.8545490751619</v>
       </c>
     </row>
     <row r="440">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>502.5045490751614</v>
+        <v>502.5045490751618</v>
       </c>
     </row>
     <row r="441">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>502.1545490751614</v>
+        <v>502.1545490751618</v>
       </c>
     </row>
     <row r="442">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>501.8045490751613</v>
+        <v>501.8045490751617</v>
       </c>
     </row>
     <row r="443">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>501.4545490751613</v>
+        <v>501.4545490751617</v>
       </c>
     </row>
     <row r="444">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751618</v>
       </c>
     </row>
     <row r="445">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>500.7545490751614</v>
+        <v>500.7545490751618</v>
       </c>
     </row>
     <row r="446">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751618</v>
       </c>
     </row>
     <row r="447">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751617</v>
       </c>
     </row>
     <row r="448">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751617</v>
       </c>
     </row>
     <row r="449">
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751619</v>
       </c>
     </row>
     <row r="450">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751611</v>
       </c>
     </row>
     <row r="451">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>499.3545490751612</v>
+        <v>499.3545490751611</v>
       </c>
     </row>
     <row r="454">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>499.0045490751612</v>
+        <v>499.0045490751613</v>
       </c>
     </row>
     <row r="455">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>498.6545490751612</v>
+        <v>498.6545490751611</v>
       </c>
     </row>
     <row r="456">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>27.84438814554655</v>
+        <v>27.84438814554652</v>
       </c>
     </row>
     <row r="546">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>80.17888814554655</v>
+        <v>80.17888814554652</v>
       </c>
     </row>
     <row r="547">
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>27.84438814554655</v>
+        <v>27.84438814554652</v>
       </c>
     </row>
     <row r="594">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>80.17888814554655</v>
+        <v>80.17888814554652</v>
       </c>
     </row>
     <row r="595">
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>4.027157958642411</v>
+        <v>4.027157958642412</v>
       </c>
     </row>
     <row r="693">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>74.88106126358036</v>
+        <v>74.88106126358035</v>
       </c>
     </row>
     <row r="786">
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>93.60132657947545</v>
+        <v>93.60132657947543</v>
       </c>
     </row>
     <row r="810">
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>93.60132657947545</v>
+        <v>93.60132657947544</v>
       </c>
     </row>
     <row r="954">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>93.60132657947545</v>
+        <v>93.60132657947544</v>
       </c>
     </row>
     <row r="978">
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>34.86535967988523</v>
+        <v>34.86535967988488</v>
       </c>
     </row>
     <row r="1012">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>139.5343596798852</v>
+        <v>139.5343596798849</v>
       </c>
     </row>
     <row r="1013">
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>244.2033596798852</v>
+        <v>244.2033596798848</v>
       </c>
     </row>
     <row r="1014">
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>348.1018721443963</v>
+        <v>348.1018721443966</v>
       </c>
     </row>
     <row r="1015">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>292.9539762776337</v>
+        <v>292.9539762776341</v>
       </c>
     </row>
     <row r="1016">
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>255.1093198690873</v>
+        <v>255.1093198690877</v>
       </c>
     </row>
     <row r="1017">
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>-70.41088521253015</v>
+        <v>-70.41088521252976</v>
       </c>
     </row>
     <row r="1021">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>-131.5014696824905</v>
+        <v>-131.5014696824901</v>
       </c>
     </row>
     <row r="1022">
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>-132.2200278564588</v>
+        <v>-132.2200278564584</v>
       </c>
     </row>
     <row r="1023">
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>-85.82206052924687</v>
+        <v>-85.82206052924663</v>
       </c>
     </row>
     <row r="1024">
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>-83.07613080100782</v>
+        <v>-83.07613080100761</v>
       </c>
     </row>
     <row r="1025">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>-128.3474865235684</v>
+        <v>-128.3474865235699</v>
       </c>
     </row>
     <row r="1026">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>-81.30415018172675</v>
+        <v>-81.30415018172626</v>
       </c>
     </row>
     <row r="1027">
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>-66.57494923805524</v>
+        <v>-66.57494923805521</v>
       </c>
     </row>
     <row r="1028">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>-43.35198707153546</v>
+        <v>-43.35198707153548</v>
       </c>
     </row>
     <row r="1029">
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>16.94364021770116</v>
+        <v>16.94364021770104</v>
       </c>
     </row>
     <row r="1030">
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>46.29754870109349</v>
+        <v>46.29754870109351</v>
       </c>
     </row>
     <row r="1031">
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>44.5941796156925</v>
+        <v>44.59417961569255</v>
       </c>
     </row>
     <row r="1032">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>79.90132272375894</v>
+        <v>79.9013227237588</v>
       </c>
     </row>
     <row r="1033">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>1308.822780425991</v>
+        <v>1308.82278042599</v>
       </c>
     </row>
     <row r="1038">
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>1585.077030042338</v>
+        <v>1585.077030042337</v>
       </c>
     </row>
     <row r="1039">
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>1618.131602829094</v>
+        <v>1618.131602829095</v>
       </c>
     </row>
     <row r="1046">
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>1438.306654837883</v>
+        <v>1438.306654837884</v>
       </c>
     </row>
     <row r="1047">
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>1315.764924980906</v>
+        <v>1315.764924980908</v>
       </c>
     </row>
     <row r="1048">
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>1198.291826634418</v>
+        <v>1198.29182663442</v>
       </c>
     </row>
     <row r="1049">
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>1029.320406265999</v>
+        <v>1029.320406265998</v>
       </c>
     </row>
     <row r="1050">
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>918.2286587817409</v>
+        <v>918.228658781742</v>
       </c>
     </row>
     <row r="1051">
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>826.1317592081856</v>
+        <v>826.1317592081861</v>
       </c>
     </row>
     <row r="1052">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>762.7374450888452</v>
+        <v>762.7374450888451</v>
       </c>
     </row>
     <row r="1053">
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>765.6984775975586</v>
+        <v>765.6984775975583</v>
       </c>
     </row>
     <row r="1054">
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>793.5659168295242</v>
+        <v>793.5659168295243</v>
       </c>
     </row>
     <row r="1055">
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>34.86535967988523</v>
+        <v>34.86535967988488</v>
       </c>
     </row>
     <row r="1060">
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>139.5343596798852</v>
+        <v>139.5343596798849</v>
       </c>
     </row>
     <row r="1061">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>244.2033596798852</v>
+        <v>244.2033596798848</v>
       </c>
     </row>
     <row r="1062">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>348.1018721443963</v>
+        <v>348.1018721443966</v>
       </c>
     </row>
     <row r="1063">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>292.9539762776337</v>
+        <v>292.9539762776341</v>
       </c>
     </row>
     <row r="1064">
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>255.1093198690873</v>
+        <v>255.1093198690877</v>
       </c>
     </row>
     <row r="1065">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>16.94364021770116</v>
+        <v>16.94364021770104</v>
       </c>
     </row>
     <row r="1078">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>46.29754870109349</v>
+        <v>46.29754870109351</v>
       </c>
     </row>
     <row r="1079">
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>44.5941796156925</v>
+        <v>44.59417961569255</v>
       </c>
     </row>
     <row r="1080">
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>79.90132272375894</v>
+        <v>79.9013227237588</v>
       </c>
     </row>
     <row r="1081">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>70.41088521253015</v>
+        <v>70.41088521252976</v>
       </c>
     </row>
     <row r="1093">
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>131.5014696824905</v>
+        <v>131.5014696824901</v>
       </c>
     </row>
     <row r="1094">
@@ -11367,7 +11367,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>132.2200278564588</v>
+        <v>132.2200278564584</v>
       </c>
     </row>
     <row r="1095">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>85.82206052924687</v>
+        <v>85.82206052924663</v>
       </c>
     </row>
     <row r="1096">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>83.07613080100782</v>
+        <v>83.07613080100761</v>
       </c>
     </row>
     <row r="1097">
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>128.3474865235684</v>
+        <v>128.3474865235699</v>
       </c>
     </row>
     <row r="1098">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>81.30415018172675</v>
+        <v>81.30415018172626</v>
       </c>
     </row>
     <row r="1099">
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>66.57494923805524</v>
+        <v>66.57494923805521</v>
       </c>
     </row>
     <row r="1100">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>43.35198707153546</v>
+        <v>43.35198707153548</v>
       </c>
     </row>
     <row r="1101">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>98.76198043324251</v>
+        <v>98.76198043324241</v>
       </c>
     </row>
     <row r="1149">
@@ -11937,7 +11937,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>75.5573811412991</v>
+        <v>75.55738114129913</v>
       </c>
     </row>
     <row r="1152">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="1161">
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1222">
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1225">
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>504.6045490751615</v>
+        <v>504.6045490751618</v>
       </c>
     </row>
     <row r="1275">
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>504.2545490751614</v>
+        <v>504.2545490751617</v>
       </c>
     </row>
     <row r="1276">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>503.9045490751615</v>
+        <v>503.9045490751618</v>
       </c>
     </row>
     <row r="1277">
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>503.5545490751614</v>
+        <v>503.5545490751617</v>
       </c>
     </row>
     <row r="1278">
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>503.2045490751614</v>
+        <v>503.2045490751618</v>
       </c>
     </row>
     <row r="1279">
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>502.8545490751615</v>
+        <v>502.8545490751619</v>
       </c>
     </row>
     <row r="1280">
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>502.5045490751614</v>
+        <v>502.5045490751618</v>
       </c>
     </row>
     <row r="1281">
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>502.1545490751614</v>
+        <v>502.1545490751618</v>
       </c>
     </row>
     <row r="1282">
@@ -13247,7 +13247,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>501.8045490751613</v>
+        <v>501.8045490751617</v>
       </c>
     </row>
     <row r="1283">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>501.4545490751613</v>
+        <v>501.4545490751617</v>
       </c>
     </row>
     <row r="1284">
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751618</v>
       </c>
     </row>
     <row r="1285">
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>500.7545490751614</v>
+        <v>500.7545490751618</v>
       </c>
     </row>
     <row r="1286">
@@ -13287,7 +13287,7 @@
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751618</v>
       </c>
     </row>
     <row r="1287">
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751617</v>
       </c>
     </row>
     <row r="1288">
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>501.1045490751613</v>
+        <v>501.1045490751617</v>
       </c>
     </row>
     <row r="1289">
@@ -13317,7 +13317,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>500.7545490751613</v>
+        <v>500.7545490751619</v>
       </c>
     </row>
     <row r="1290">
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>500.4045490751613</v>
+        <v>500.4045490751611</v>
       </c>
     </row>
     <row r="1291">
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>499.3545490751612</v>
+        <v>499.3545490751611</v>
       </c>
     </row>
     <row r="1294">
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>499.0045490751612</v>
+        <v>499.0045490751613</v>
       </c>
     </row>
     <row r="1295">
@@ -13377,7 +13377,7 @@
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>498.6545490751612</v>
+        <v>498.6545490751611</v>
       </c>
     </row>
     <row r="1296">
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>428.9138667138873</v>
+        <v>428.9138667138875</v>
       </c>
     </row>
     <row r="1299">
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>428.6163667138872</v>
+        <v>428.6163667138874</v>
       </c>
     </row>
     <row r="1300">
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>428.3188667138872</v>
+        <v>428.3188667138875</v>
       </c>
     </row>
     <row r="1301">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>428.0213667138872</v>
+        <v>428.0213667138875</v>
       </c>
     </row>
     <row r="1302">
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>427.7238667138872</v>
+        <v>427.7238667138876</v>
       </c>
     </row>
     <row r="1303">
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>427.4263667138873</v>
+        <v>427.4263667138876</v>
       </c>
     </row>
     <row r="1304">
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>427.1288667138871</v>
+        <v>427.1288667138875</v>
       </c>
     </row>
     <row r="1305">
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>426.8313667138871</v>
+        <v>426.8313667138875</v>
       </c>
     </row>
     <row r="1306">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>426.5338667138871</v>
+        <v>426.5338667138874</v>
       </c>
     </row>
     <row r="1307">
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>426.236366713887</v>
+        <v>426.2363667138874</v>
       </c>
     </row>
     <row r="1308">
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138875</v>
       </c>
     </row>
     <row r="1309">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>425.6413667138872</v>
+        <v>425.6413667138875</v>
       </c>
     </row>
     <row r="1310">
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138875</v>
       </c>
     </row>
     <row r="1311">
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138874</v>
       </c>
     </row>
     <row r="1312">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="B1312" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138874</v>
       </c>
     </row>
     <row r="1313">
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138876</v>
       </c>
     </row>
     <row r="1314">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138869</v>
       </c>
     </row>
     <row r="1315">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>424.451366713887</v>
+        <v>424.4513667138869</v>
       </c>
     </row>
     <row r="1318">
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138871</v>
       </c>
     </row>
     <row r="1319">
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>423.856366713887</v>
+        <v>423.8563667138869</v>
       </c>
     </row>
     <row r="1320">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138869</v>
       </c>
     </row>
     <row r="1321">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>52.41956809739886</v>
+        <v>52.41956809739888</v>
       </c>
     </row>
     <row r="1358">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>84.51068867202336</v>
+        <v>84.51068867202339</v>
       </c>
     </row>
     <row r="1363">
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>91.87611364796857</v>
+        <v>91.87611364796858</v>
       </c>
     </row>
     <row r="1365">
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1365" t="n">
-        <v>177.6113371677765</v>
+        <v>181.1238486451562</v>
       </c>
     </row>
     <row r="1366">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>74.62303877925618</v>
+        <v>79.73526514166298</v>
       </c>
     </row>
     <row r="1367">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>44.55663288278903</v>
+        <v>44.55663288278905</v>
       </c>
     </row>
     <row r="1406">
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>71.83408537121986</v>
+        <v>71.83408537121989</v>
       </c>
     </row>
     <row r="1411">
@@ -14547,7 +14547,7 @@
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>78.09469660077328</v>
+        <v>78.09469660077329</v>
       </c>
     </row>
     <row r="1413">
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>150.96963659261</v>
+        <v>153.9552713483828</v>
       </c>
     </row>
     <row r="1414">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>63.42958296236775</v>
+        <v>67.77497537041353</v>
       </c>
     </row>
     <row r="1415">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>428.9138667138873</v>
+        <v>428.9138667138875</v>
       </c>
     </row>
     <row r="1443">
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>428.6163667138872</v>
+        <v>428.6163667138874</v>
       </c>
     </row>
     <row r="1444">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>428.3188667138872</v>
+        <v>428.3188667138875</v>
       </c>
     </row>
     <row r="1445">
@@ -14877,7 +14877,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>428.0213667138872</v>
+        <v>428.0213667138875</v>
       </c>
     </row>
     <row r="1446">
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>427.7238667138872</v>
+        <v>427.7238667138876</v>
       </c>
     </row>
     <row r="1447">
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>427.4263667138873</v>
+        <v>427.4263667138876</v>
       </c>
     </row>
     <row r="1448">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>427.1288667138871</v>
+        <v>427.1288667138875</v>
       </c>
     </row>
     <row r="1449">
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>426.8313667138871</v>
+        <v>426.8313667138875</v>
       </c>
     </row>
     <row r="1450">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>426.5338667138871</v>
+        <v>426.5338667138874</v>
       </c>
     </row>
     <row r="1451">
@@ -14937,7 +14937,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>426.236366713887</v>
+        <v>426.2363667138874</v>
       </c>
     </row>
     <row r="1452">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138875</v>
       </c>
     </row>
     <row r="1453">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>425.6413667138872</v>
+        <v>425.6413667138875</v>
       </c>
     </row>
     <row r="1454">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138875</v>
       </c>
     </row>
     <row r="1455">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138874</v>
       </c>
     </row>
     <row r="1456">
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1456" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138874</v>
       </c>
     </row>
     <row r="1457">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138876</v>
       </c>
     </row>
     <row r="1458">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138869</v>
       </c>
     </row>
     <row r="1459">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>424.451366713887</v>
+        <v>424.4513667138869</v>
       </c>
     </row>
     <row r="1462">
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138871</v>
       </c>
     </row>
     <row r="1463">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>423.856366713887</v>
+        <v>423.8563667138869</v>
       </c>
     </row>
     <row r="1464">
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="B1464" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138869</v>
       </c>
     </row>
     <row r="1465">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>428.9138667138873</v>
+        <v>428.9138667138875</v>
       </c>
     </row>
     <row r="1467">
@@ -15097,7 +15097,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>428.6163667138872</v>
+        <v>428.6163667138874</v>
       </c>
     </row>
     <row r="1468">
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>428.3188667138872</v>
+        <v>428.3188667138875</v>
       </c>
     </row>
     <row r="1469">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>428.0213667138872</v>
+        <v>428.0213667138875</v>
       </c>
     </row>
     <row r="1470">
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>427.7238667138872</v>
+        <v>427.7238667138876</v>
       </c>
     </row>
     <row r="1471">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>427.4263667138873</v>
+        <v>427.4263667138876</v>
       </c>
     </row>
     <row r="1472">
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>427.1288667138871</v>
+        <v>427.1288667138875</v>
       </c>
     </row>
     <row r="1473">
@@ -15157,7 +15157,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>426.8313667138871</v>
+        <v>426.8313667138875</v>
       </c>
     </row>
     <row r="1474">
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>426.5338667138871</v>
+        <v>426.5338667138874</v>
       </c>
     </row>
     <row r="1475">
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>426.236366713887</v>
+        <v>426.2363667138874</v>
       </c>
     </row>
     <row r="1476">
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138875</v>
       </c>
     </row>
     <row r="1477">
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>425.6413667138872</v>
+        <v>425.6413667138875</v>
       </c>
     </row>
     <row r="1478">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138875</v>
       </c>
     </row>
     <row r="1479">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138874</v>
       </c>
     </row>
     <row r="1480">
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="B1480" t="n">
-        <v>425.9388667138871</v>
+        <v>425.9388667138874</v>
       </c>
     </row>
     <row r="1481">
@@ -15237,7 +15237,7 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>425.6413667138871</v>
+        <v>425.6413667138876</v>
       </c>
     </row>
     <row r="1482">
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>425.3438667138871</v>
+        <v>425.3438667138869</v>
       </c>
     </row>
     <row r="1483">
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>424.451366713887</v>
+        <v>424.4513667138869</v>
       </c>
     </row>
     <row r="1486">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="B1486" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138871</v>
       </c>
     </row>
     <row r="1487">
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>423.856366713887</v>
+        <v>423.8563667138869</v>
       </c>
     </row>
     <row r="1488">
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>424.153866713887</v>
+        <v>424.1538667138869</v>
       </c>
     </row>
     <row r="1489">
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="B1514" t="n">
-        <v>592.7054704343395</v>
+        <v>592.7054704343393</v>
       </c>
     </row>
     <row r="1515">
@@ -15577,7 +15577,7 @@
         </is>
       </c>
       <c r="B1515" t="n">
-        <v>643.036015280998</v>
+        <v>643.0360152809973</v>
       </c>
     </row>
     <row r="1516">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>751.9595746279465</v>
+        <v>751.9595746279457</v>
       </c>
     </row>
     <row r="1517">
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>861.8805211797696</v>
+        <v>861.8805211797688</v>
       </c>
     </row>
     <row r="1518">
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1521" t="n">
-        <v>845.862874175202</v>
+        <v>845.8628741752016</v>
       </c>
     </row>
     <row r="1522">
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="B1522" t="n">
-        <v>885.4436160778114</v>
+        <v>885.4436160778109</v>
       </c>
     </row>
     <row r="1523">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="B1523" t="n">
-        <v>989.7137159572781</v>
+        <v>989.7137159572776</v>
       </c>
     </row>
     <row r="1524">
@@ -16047,7 +16047,7 @@
         </is>
       </c>
       <c r="B1562" t="n">
-        <v>160.5589263391056</v>
+        <v>160.5589263391053</v>
       </c>
     </row>
     <row r="1563">
@@ -16057,7 +16057,7 @@
         </is>
       </c>
       <c r="B1563" t="n">
-        <v>212.8510599987407</v>
+        <v>212.8510599987399</v>
       </c>
     </row>
     <row r="1564">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="B1564" t="n">
-        <v>332.0424853742531</v>
+        <v>332.0424853742524</v>
       </c>
     </row>
     <row r="1565">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="B1565" t="n">
-        <v>445.123370561833</v>
+        <v>445.1233705618322</v>
       </c>
     </row>
     <row r="1566">
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="B1569" t="n">
-        <v>167.9646775880452</v>
+        <v>167.9646775880448</v>
       </c>
     </row>
     <row r="1570">
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="B1570" t="n">
-        <v>192.8645283074313</v>
+        <v>192.8645283074308</v>
       </c>
     </row>
     <row r="1571">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="B1571" t="n">
-        <v>228.4964561948661</v>
+        <v>228.4964561948656</v>
       </c>
     </row>
     <row r="1572">
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="B1578" t="n">
-        <v>135.0551638882177</v>
+        <v>135.0551638882176</v>
       </c>
     </row>
     <row r="1579">
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="B1586" t="n">
-        <v>160.5589263391056</v>
+        <v>160.5589263391053</v>
       </c>
     </row>
     <row r="1587">
@@ -16297,7 +16297,7 @@
         </is>
       </c>
       <c r="B1587" t="n">
-        <v>212.8510599987407</v>
+        <v>212.8510599987399</v>
       </c>
     </row>
     <row r="1588">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="B1588" t="n">
-        <v>332.0424853742531</v>
+        <v>332.0424853742524</v>
       </c>
     </row>
     <row r="1589">
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="B1589" t="n">
-        <v>445.123370561833</v>
+        <v>445.1233705618322</v>
       </c>
     </row>
     <row r="1590">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="B1593" t="n">
-        <v>167.9646775880452</v>
+        <v>167.9646775880448</v>
       </c>
     </row>
     <row r="1594">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="B1594" t="n">
-        <v>192.8645283074313</v>
+        <v>192.8645283074308</v>
       </c>
     </row>
     <row r="1595">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="B1595" t="n">
-        <v>228.4964561948661</v>
+        <v>228.4964561948656</v>
       </c>
     </row>
     <row r="1596">
@@ -16447,7 +16447,7 @@
         </is>
       </c>
       <c r="B1602" t="n">
-        <v>135.0551638882177</v>
+        <v>135.0551638882176</v>
       </c>
     </row>
     <row r="1603">
@@ -16527,7 +16527,7 @@
         </is>
       </c>
       <c r="B1610" t="n">
-        <v>160.5589263391056</v>
+        <v>160.5589263391053</v>
       </c>
     </row>
     <row r="1611">
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="B1611" t="n">
-        <v>212.8510599987407</v>
+        <v>212.8510599987399</v>
       </c>
     </row>
     <row r="1612">
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="B1612" t="n">
-        <v>332.0424853742531</v>
+        <v>332.0424853742524</v>
       </c>
     </row>
     <row r="1613">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="B1613" t="n">
-        <v>445.123370561833</v>
+        <v>445.1233705618322</v>
       </c>
     </row>
     <row r="1614">
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="B1617" t="n">
-        <v>167.9646775880452</v>
+        <v>167.9646775880448</v>
       </c>
     </row>
     <row r="1618">
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="B1618" t="n">
-        <v>192.8645283074313</v>
+        <v>192.8645283074308</v>
       </c>
     </row>
     <row r="1619">
@@ -16617,7 +16617,7 @@
         </is>
       </c>
       <c r="B1619" t="n">
-        <v>228.4964561948661</v>
+        <v>228.4964561948656</v>
       </c>
     </row>
     <row r="1620">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="B1626" t="n">
-        <v>135.0551638882177</v>
+        <v>135.0551638882176</v>
       </c>
     </row>
     <row r="1627">
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="B1658" t="n">
-        <v>128.4471410712845</v>
+        <v>128.4471410712842</v>
       </c>
     </row>
     <row r="1659">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="B1659" t="n">
-        <v>170.2808479989926</v>
+        <v>170.280847998992</v>
       </c>
     </row>
     <row r="1660">
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="B1660" t="n">
-        <v>265.6339882994025</v>
+        <v>265.6339882994019</v>
       </c>
     </row>
     <row r="1661">
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="B1661" t="n">
-        <v>356.0986964494664</v>
+        <v>356.0986964494658</v>
       </c>
     </row>
     <row r="1662">
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="B1665" t="n">
-        <v>134.3717420704362</v>
+        <v>134.3717420704358</v>
       </c>
     </row>
     <row r="1666">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="B1666" t="n">
-        <v>154.2916226459451</v>
+        <v>154.2916226459447</v>
       </c>
     </row>
     <row r="1667">
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="B1667" t="n">
-        <v>182.7971649558929</v>
+        <v>182.7971649558925</v>
       </c>
     </row>
     <row r="1668">
@@ -17167,7 +17167,7 @@
         </is>
       </c>
       <c r="B1674" t="n">
-        <v>108.0441311105742</v>
+        <v>108.0441311105741</v>
       </c>
     </row>
     <row r="1675">
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="B1797" t="n">
-        <v>10.77060040386539</v>
+        <v>7.258088926485777</v>
       </c>
     </row>
     <row r="1798">
@@ -18407,7 +18407,7 @@
         </is>
       </c>
       <c r="B1798" t="n">
-        <v>44.07076801970052</v>
+        <v>38.95854165729371</v>
       </c>
     </row>
     <row r="1799">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="B1845" t="n">
-        <v>0</v>
+        <v>5.620018363807383</v>
       </c>
     </row>
     <row r="1846">
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="B1846" t="n">
-        <v>0</v>
+        <v>8.17956217985088</v>
       </c>
     </row>
     <row r="1847">
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="B1898" t="n">
-        <v>128.4471410712845</v>
+        <v>128.4471410712842</v>
       </c>
     </row>
     <row r="1899">
@@ -19417,7 +19417,7 @@
         </is>
       </c>
       <c r="B1899" t="n">
-        <v>170.2808479989926</v>
+        <v>170.280847998992</v>
       </c>
     </row>
     <row r="1900">
@@ -19427,7 +19427,7 @@
         </is>
       </c>
       <c r="B1900" t="n">
-        <v>265.6339882994025</v>
+        <v>265.6339882994019</v>
       </c>
     </row>
     <row r="1901">
@@ -19437,7 +19437,7 @@
         </is>
       </c>
       <c r="B1901" t="n">
-        <v>356.0986964494664</v>
+        <v>356.0986964494658</v>
       </c>
     </row>
     <row r="1902">
@@ -19477,7 +19477,7 @@
         </is>
       </c>
       <c r="B1905" t="n">
-        <v>134.3717420704362</v>
+        <v>134.3717420704358</v>
       </c>
     </row>
     <row r="1906">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="B1906" t="n">
-        <v>154.2916226459451</v>
+        <v>154.2916226459447</v>
       </c>
     </row>
     <row r="1907">
@@ -19497,7 +19497,7 @@
         </is>
       </c>
       <c r="B1907" t="n">
-        <v>182.7971649558929</v>
+        <v>182.7971649558925</v>
       </c>
     </row>
     <row r="1908">
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="B1914" t="n">
-        <v>108.0441311105742</v>
+        <v>108.0441311105741</v>
       </c>
     </row>
     <row r="1915">
@@ -19647,7 +19647,7 @@
         </is>
       </c>
       <c r="B1922" t="n">
-        <v>128.4471410712845</v>
+        <v>128.4471410712842</v>
       </c>
     </row>
     <row r="1923">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="B1923" t="n">
-        <v>170.2808479989926</v>
+        <v>170.280847998992</v>
       </c>
     </row>
     <row r="1924">
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="B1924" t="n">
-        <v>265.6339882994025</v>
+        <v>265.6339882994019</v>
       </c>
     </row>
     <row r="1925">
@@ -19677,7 +19677,7 @@
         </is>
       </c>
       <c r="B1925" t="n">
-        <v>356.0986964494664</v>
+        <v>356.0986964494658</v>
       </c>
     </row>
     <row r="1926">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="B1929" t="n">
-        <v>134.3717420704362</v>
+        <v>134.3717420704358</v>
       </c>
     </row>
     <row r="1930">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B1930" t="n">
-        <v>154.2916226459451</v>
+        <v>154.2916226459447</v>
       </c>
     </row>
     <row r="1931">
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="B1931" t="n">
-        <v>182.7971649558929</v>
+        <v>182.7971649558925</v>
       </c>
     </row>
     <row r="1932">
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="B1938" t="n">
-        <v>108.0441311105742</v>
+        <v>108.0441311105741</v>
       </c>
     </row>
     <row r="1939">
@@ -21197,7 +21197,7 @@
         </is>
       </c>
       <c r="B2077" t="n">
-        <v>324.3016548725679</v>
+        <v>324.301654872568</v>
       </c>
     </row>
     <row r="2078">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="B2085" t="n">
-        <v>403.7798935151414</v>
+        <v>403.7798935151415</v>
       </c>
     </row>
     <row r="2086">
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="B2181" t="n">
-        <v>82.51400641615365</v>
+        <v>82.51400641615362</v>
       </c>
     </row>
     <row r="2182">
@@ -22247,7 +22247,7 @@
         </is>
       </c>
       <c r="B2182" t="n">
-        <v>73.05392248640803</v>
+        <v>73.05392248640806</v>
       </c>
     </row>
     <row r="2183">
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="B2184" t="n">
-        <v>75.54662605674693</v>
+        <v>75.54662605674694</v>
       </c>
     </row>
     <row r="2185">
@@ -23187,7 +23187,7 @@
         </is>
       </c>
       <c r="B2276" t="n">
-        <v>-122.0643962269677</v>
+        <v>-122.0643962269676</v>
       </c>
     </row>
     <row r="2277">
@@ -23837,7 +23837,7 @@
         </is>
       </c>
       <c r="B2341" t="n">
-        <v>60.98912205046106</v>
+        <v>60.98912205046108</v>
       </c>
     </row>
     <row r="2342">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="B2346" t="n">
-        <v>84.12603209107843</v>
+        <v>84.12603209107846</v>
       </c>
     </row>
     <row r="2347">
@@ -23907,7 +23907,7 @@
         </is>
       </c>
       <c r="B2348" t="n">
-        <v>94.74128896994013</v>
+        <v>94.74128896994014</v>
       </c>
     </row>
     <row r="2349">
@@ -23917,7 +23917,7 @@
         </is>
       </c>
       <c r="B2349" t="n">
-        <v>172.3210489346841</v>
+        <v>175.3066836904569</v>
       </c>
     </row>
     <row r="2350">
@@ -23927,7 +23927,7 @@
         </is>
       </c>
       <c r="B2350" t="n">
-        <v>110.3779617653609</v>
+        <v>114.7233541734067</v>
       </c>
     </row>
     <row r="2351">
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="B2372" t="n">
-        <v>25.60495789009991</v>
+        <v>25.60495789009981</v>
       </c>
     </row>
     <row r="2373">
@@ -24157,7 +24157,7 @@
         </is>
       </c>
       <c r="B2373" t="n">
-        <v>23.25988388184635</v>
+        <v>28.87990224565376</v>
       </c>
     </row>
     <row r="2374">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="B2374" t="n">
-        <v>17.38931069039197</v>
+        <v>25.56887287024282</v>
       </c>
     </row>
     <row r="2375">
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="B2375" t="n">
-        <v>30.55988092004693</v>
+        <v>30.55988092004696</v>
       </c>
     </row>
     <row r="2376">
@@ -24187,7 +24187,7 @@
         </is>
       </c>
       <c r="B2376" t="n">
-        <v>26.44131911986143</v>
+        <v>26.44131911986142</v>
       </c>
     </row>
     <row r="2377">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="B2394" t="n">
-        <v>1.224175098750766</v>
+        <v>1.224175098750765</v>
       </c>
     </row>
     <row r="2395">
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="B2417" t="n">
-        <v>3.528000000000002</v>
+        <v>3.528000000000001</v>
       </c>
     </row>
     <row r="2418">
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="B2431" t="n">
-        <v>170.3191767084894</v>
+        <v>170.3191767084893</v>
       </c>
     </row>
     <row r="2432">
@@ -25107,7 +25107,7 @@
         </is>
       </c>
       <c r="B2468" t="n">
-        <v>122.0643962269677</v>
+        <v>122.0643962269676</v>
       </c>
     </row>
     <row r="2469">
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="B2533" t="n">
-        <v>60.98912205046106</v>
+        <v>60.98912205046108</v>
       </c>
     </row>
     <row r="2534">
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="B2538" t="n">
-        <v>84.12603209107843</v>
+        <v>84.12603209107846</v>
       </c>
     </row>
     <row r="2539">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="B2540" t="n">
-        <v>94.74128896994013</v>
+        <v>94.74128896994014</v>
       </c>
     </row>
     <row r="2541">
@@ -25837,7 +25837,7 @@
         </is>
       </c>
       <c r="B2541" t="n">
-        <v>172.3210489346841</v>
+        <v>175.3066836904569</v>
       </c>
     </row>
     <row r="2542">
@@ -25847,7 +25847,7 @@
         </is>
       </c>
       <c r="B2542" t="n">
-        <v>110.3779617653609</v>
+        <v>114.7233541734067</v>
       </c>
     </row>
     <row r="2543">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="B2564" t="n">
-        <v>25.60495789009991</v>
+        <v>25.60495789009981</v>
       </c>
     </row>
     <row r="2565">
@@ -26077,7 +26077,7 @@
         </is>
       </c>
       <c r="B2565" t="n">
-        <v>28.87990224565377</v>
+        <v>28.87990224565376</v>
       </c>
     </row>
     <row r="2566">
@@ -26087,7 +26087,7 @@
         </is>
       </c>
       <c r="B2566" t="n">
-        <v>25.56887287024281</v>
+        <v>25.56887287024282</v>
       </c>
     </row>
     <row r="2567">
@@ -26097,7 +26097,7 @@
         </is>
       </c>
       <c r="B2567" t="n">
-        <v>30.55988092004693</v>
+        <v>30.55988092004696</v>
       </c>
     </row>
     <row r="2568">
